--- a/超神机械师_职业链设定表.xlsx
+++ b/超神机械师_职业链设定表.xlsx
@@ -33,10 +33,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -47,24 +47,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-        <bgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,21 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,10 +445,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,17 +482,17 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>机械入门者</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>机械系入门者</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>机械系入门者</t>
         </is>
@@ -534,17 +507,17 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>机械师学徒</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>枪炮师学徒</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>械武者学徒</t>
         </is>
@@ -559,17 +532,17 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>见习机械师</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>见习枪炮师</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>见习械武者</t>
         </is>
@@ -584,17 +557,17 @@
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>磁环机械师</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>精准枪炮师</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>殖装械武者</t>
         </is>
@@ -609,17 +582,17 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>数据机械师</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>火力枪炮师</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>格斗械武者</t>
         </is>
@@ -634,17 +607,17 @@
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>战争机械师</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>重炮枪炮师</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>战技械武者</t>
         </is>
@@ -659,19 +632,19 @@
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>虚拟机械师</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>战争堡垒（原著）</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>机甲操控师（原著）</t>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>战争堡垒</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>机甲操控师</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -684,17 +657,17 @@
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>星海机械师</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>阶位+枪炮师</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>阶位+械武者</t>
         </is>
@@ -709,17 +682,17 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>真理机械师</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>阶位+枪炮师</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>阶位+械武者</t>
         </is>
@@ -734,17 +707,17 @@
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>使徒机械师</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>阶位+枪炮师</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>阶位+械武者</t>
         </is>
@@ -759,17 +732,17 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>帝皇机械师</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>阶位+枪炮师</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>阶位+械武者</t>
         </is>
@@ -784,24 +757,24 @@
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>主宰机械师</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>阶位+枪炮师</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>阶位+械武者</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>ch861</t>
+          <t>ch864</t>
         </is>
       </c>
     </row>
@@ -809,17 +782,17 @@
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>神座机械师</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>阶位+枪炮师</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>阶位+械武者</t>
         </is>
@@ -834,17 +807,17 @@
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>超神机械师</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>阶位+枪炮师</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>阶位+械武者</t>
         </is>
@@ -1291,11 +1264,11 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1471,12 +1444,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1492,6 +1466,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>原著出处</t>
         </is>
       </c>
@@ -1509,6 +1488,11 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>武装/操控/能量三支五层</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>ch50</t>
         </is>
       </c>
@@ -1526,6 +1510,11 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>ch50</t>
         </is>
       </c>
@@ -1543,6 +1532,11 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>威力/持久/操控三维度</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>ch50</t>
         </is>
       </c>
@@ -1560,7 +1554,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ch50</t>
+          <t>7分支15法术</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ch410</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1576,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ch50</t>
+          <t>心智/念动/感应</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ch1384</t>
         </is>
       </c>
     </row>
@@ -1592,13 +1596,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1622,6 +1627,11 @@
           <t>说明</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>原著出处</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1632,14 +1642,17 @@
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1~2</t>
+        </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>最低级超能者</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1650,190 +1663,314 @@
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>100</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ch3原文确认</t>
+          <t>气力护体可防狙击子弹</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>ch3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E+</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>独自抵挡小型武装部队</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>ch3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>徒手拆楼，正面对抗军队</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>ch3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>10000</v>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>天灾级</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10000~33000</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>天灾级，1万掀起弱天灾，2万以上可毁灭行星表面</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>ch3</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>S（超A）</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>52000</v>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>20000~33000</t>
+        </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>宇宙顶级</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S（超A）</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>星系级</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>底线常态一击爆星</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ch3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SS（巅峰超A）</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>星团级</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>X（超神）</t>
+          <t>SS（巅峰超A）</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>140000</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>神性蜕变触发</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>ch1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>X（超神）</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>148800+</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>无上限，概念永生</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>ch1396</t>
         </is>
@@ -1850,12 +1987,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1931,7 +2069,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -1946,7 +2084,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -1957,11 +2095,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>第六级分水岭·气力属性强化</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -1972,11 +2115,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -1987,11 +2130,11 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1600</v>
+        <v>3000</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2002,11 +2145,11 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2200</v>
+        <v>5000</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2017,11 +2160,11 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2032,11 +2175,15 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>插值</t>
+        <v>10000</v>
+      </c>
+      <c r="C12" s="2">
+        <f>A阶门槛</f>
+        <v/>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2047,11 +2194,11 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>5500</v>
+        <v>20000</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2062,11 +2209,11 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7500</v>
+        <v>30000</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2077,11 +2224,11 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>插值（=A阶门槛）</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2092,11 +2239,11 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>14000</v>
+        <v>50000</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2107,11 +2254,11 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>19000</v>
+        <v>60000</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2122,11 +2269,11 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>25000</v>
+        <v>80000</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2137,11 +2284,11 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>32000</v>
+        <v>100000</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2152,11 +2299,11 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2167,11 +2314,11 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2182,11 +2329,16 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>78000</v>
+        <v>180000</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ch626（神性蜕变触发）</t>
+          <t>神性蜕变触发</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ch626</t>
         </is>
       </c>
     </row>
@@ -2196,8 +2348,10 @@
           <t>Lv22</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>100000</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -2211,8 +2365,10 @@
           <t>Lv23</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>130000</v>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -2226,8 +2382,10 @@
           <t>Lv24</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>170000</v>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -2242,11 +2400,11 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>220000</v>
+        <v>290000</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>插值</t>
+          <t>ch3</t>
         </is>
       </c>
     </row>
@@ -2256,8 +2414,10 @@
           <t>Lv26</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>280000</v>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -2271,8 +2431,10 @@
           <t>Lv27</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
-        <v>350000</v>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -2286,8 +2448,10 @@
           <t>Lv28</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
-        <v>420000</v>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -2302,11 +2466,16 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>481200</v>
+        <v>480000</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>韩萧最终面板</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>ch1402</t>
         </is>
       </c>
     </row>
